--- a/Data to learn Lookup.xlsx
+++ b/Data to learn Lookup.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Om Computers\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5FA5504-CFEC-4082-9AC4-5E6485DDEDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{271C7367-B856-4155-97A1-252527CE6A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B458A35D-FE5A-4D24-989A-C9AAF29B9388}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales" sheetId="1" r:id="rId1"/>
-    <sheet name="products" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="products" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="106">
   <si>
     <t>Order_ID</t>
   </si>
@@ -302,6 +326,174 @@
       <t>Actual Price vs Standard Price</t>
     </r>
   </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syntax </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Lookup </t>
+  </si>
+  <si>
+    <t>lookup(lookup_value , lookup_vector , [Result_vector])</t>
+  </si>
+  <si>
+    <t>2. V-lookup</t>
+  </si>
+  <si>
+    <t>vlookup( lookup_value , Table_array , col_index_number , [Range_lookup])</t>
+  </si>
+  <si>
+    <t>3. H-lookup</t>
+  </si>
+  <si>
+    <t>hlookup( lookup_value , Table_array , Row_index_number , [Range_lookup])</t>
+  </si>
+  <si>
+    <t>4. X-lookup</t>
+  </si>
+  <si>
+    <t>Emp_id</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Sakshi</t>
+  </si>
+  <si>
+    <t>Ritik</t>
+  </si>
+  <si>
+    <t>Manas</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Noida</t>
+  </si>
+  <si>
+    <t>XLOOKUP(lookup_value , lookup_array , return_array , [if_not_found] , [match_mode] , [search_mode])</t>
+  </si>
+  <si>
+    <t>product_names</t>
+  </si>
+  <si>
+    <t>P106</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>1. if</t>
+  </si>
+  <si>
+    <t>if(logic_test , value_if_true , value_if_false)</t>
+  </si>
+  <si>
+    <t>2. ifs</t>
+  </si>
+  <si>
+    <t>ifs(logic_test1 , value_if_true1 , logic_test2 , value_if_true2 , logic_test3 , value_if_true3 , ….................)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A and B</t>
+  </si>
+  <si>
+    <t>A or B</t>
+  </si>
+  <si>
+    <t>Not A</t>
+  </si>
+  <si>
+    <t>Not B</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Voting eligibility</t>
+  </si>
+  <si>
+    <t>Nationality</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>orders cateogry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditional </t>
+  </si>
+  <si>
+    <t>Sumif</t>
+  </si>
+  <si>
+    <t>sumif(range , criteria , [ sum_range])</t>
+  </si>
+  <si>
+    <t>Payment_mode</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One condition </t>
+  </si>
+  <si>
+    <t>Sumifs</t>
+  </si>
+  <si>
+    <t>Multiple conditions</t>
+  </si>
+  <si>
+    <t>sumifs( sum_of_value , cretiria_range1 , criteria1 , creteria_range2 , criteria2 , ….............)</t>
+  </si>
+  <si>
+    <t>countif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">countifs </t>
+  </si>
+  <si>
+    <t>countif(range, criteria)</t>
+  </si>
+  <si>
+    <t>Number of Observations for certain crietia</t>
+  </si>
+  <si>
+    <t>countifs( range1, criteria1, range2 , creitia2 , ….....)</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +524,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -340,11 +532,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -352,11 +559,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="22">
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -390,6 +603,18 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -460,20 +685,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3CFB0FF-5878-48F6-ACCE-FDC5CA3B7298}" name="Table1" displayName="Table1" ref="A1:K9" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:K9" xr:uid="{C3CFB0FF-5878-48F6-ACCE-FDC5CA3B7298}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F1D12655-05F0-4790-8F75-80A9D87C7187}" name="Order_ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{EFF7E960-CB2D-426E-AEE5-6EDAEEF3FD28}" name="Customer_Name" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{79FA486E-BA82-4913-BCE7-F6EE22BB6A3B}" name="City" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{F6AB74CE-F9FB-4E09-968A-510E21334581}" name="Product_ID" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{E2AE74AF-D1F1-4F7F-9829-A2BBD1C496D8}" name="Product_Name" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{7066B73D-45C2-476F-BD9E-270EBD0CB1C1}" name="Category" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{A7A4DEE5-BC6C-4705-950E-090DD5F0C425}" name="Quantity" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{D91DD328-CB85-47A1-AF2B-77F31B55DF30}" name="Price" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{99BD8EBD-4739-4727-BD0D-7D0767EB1D0E}" name="Total_Amount" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{6B881ECD-471C-4D2D-BA69-98C7D0F6A1A5}" name="Payment_Mode" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{039C0167-425F-4AD6-8FC5-CAE26612DE90}" name="Order_Status" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3CFB0FF-5878-48F6-ACCE-FDC5CA3B7298}" name="Table1" displayName="Table1" ref="A1:N9" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:N9" xr:uid="{C3CFB0FF-5878-48F6-ACCE-FDC5CA3B7298}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{F1D12655-05F0-4790-8F75-80A9D87C7187}" name="Order_ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{EFF7E960-CB2D-426E-AEE5-6EDAEEF3FD28}" name="Customer_Name" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{79FA486E-BA82-4913-BCE7-F6EE22BB6A3B}" name="City" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{F6AB74CE-F9FB-4E09-968A-510E21334581}" name="Product_ID" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{E2AE74AF-D1F1-4F7F-9829-A2BBD1C496D8}" name="Product_Name" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{7066B73D-45C2-476F-BD9E-270EBD0CB1C1}" name="Category" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{A7A4DEE5-BC6C-4705-950E-090DD5F0C425}" name="Quantity" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{D91DD328-CB85-47A1-AF2B-77F31B55DF30}" name="Price" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{99BD8EBD-4739-4727-BD0D-7D0767EB1D0E}" name="Total_Amount" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{6B881ECD-471C-4D2D-BA69-98C7D0F6A1A5}" name="Payment_Mode" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{039C0167-425F-4AD6-8FC5-CAE26612DE90}" name="Order_Status" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{2E322447-67C8-4C89-B026-7ED19373D603}" name="product_names" dataDxfId="8">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{D65D32E8-F811-42A5-A11C-704B84801F2D}" name="Column1" dataDxfId="7">
+      <calculatedColumnFormula>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{29537D5D-15A3-46D9-9369-18E6F7D3F363}" name="orders cateogry" dataDxfId="6">
+      <calculatedColumnFormula array="1">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -789,21 +1023,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A74982-0780-42AB-8BA1-41550DBB81A1}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.36328125" customWidth="1"/>
     <col min="4" max="4" width="12.26953125" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" customWidth="1"/>
-    <col min="6" max="6" width="10.26953125" customWidth="1"/>
+    <col min="5" max="5" width="8.36328125" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.1796875" customWidth="1"/>
-    <col min="9" max="9" width="14.90625" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.1796875" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,8 +1074,17 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1001</v>
       </c>
@@ -872,8 +1118,24 @@
       <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L2" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>Laptop</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>Profitable_order</v>
+      </c>
+      <c r="N2" s="2" t="str" cm="1">
+        <f t="array" ref="N2">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>High Sales</v>
+      </c>
+      <c r="P2" t="str" cm="1">
+        <f t="array" ref="P2">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt;0, "Negative Sales")</f>
+        <v>High Sales</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
@@ -907,8 +1169,24 @@
       <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>Mobile</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>Profitable_order</v>
+      </c>
+      <c r="N3" s="2" t="str" cm="1">
+        <f t="array" ref="N3">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>High Sales</v>
+      </c>
+      <c r="P3" t="str" cm="1">
+        <f t="array" ref="P3">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt; 0, "Negative Sales")</f>
+        <v>High Sales</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>1003</v>
       </c>
@@ -916,7 +1194,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
@@ -942,8 +1220,24 @@
       <c r="K4" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L4" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>Shoes</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>Profitable_order</v>
+      </c>
+      <c r="N4" s="2" t="str" cm="1">
+        <f t="array" ref="N4">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>Low Sales</v>
+      </c>
+      <c r="P4" t="str" cm="1">
+        <f t="array" ref="P4">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt; 0, "Negative Sales")</f>
+        <v>Low Sales</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>1004</v>
       </c>
@@ -954,7 +1248,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>32</v>
@@ -977,8 +1271,24 @@
       <c r="K5" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>Product does not exist</v>
+      </c>
+      <c r="M5" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>incomplete order</v>
+      </c>
+      <c r="N5" s="2" t="str" cm="1">
+        <f t="array" ref="N5">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>Low Sales</v>
+      </c>
+      <c r="P5" t="str" cm="1">
+        <f t="array" ref="P5">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt; 0, "Negative Sales")</f>
+        <v>Low Sales</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>1005</v>
       </c>
@@ -1004,7 +1314,7 @@
         <v>500</v>
       </c>
       <c r="I6" s="2">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>22</v>
@@ -1012,8 +1322,24 @@
       <c r="K6" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L6" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>T-Shirt</v>
+      </c>
+      <c r="M6" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>Profitable_order</v>
+      </c>
+      <c r="N6" s="2" t="str" cm="1">
+        <f t="array" ref="N6">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>Low Sales</v>
+      </c>
+      <c r="P6" t="str" cm="1">
+        <f t="array" ref="P6">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt; 0, "Negative Sales")</f>
+        <v>Low Sales</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>1006</v>
       </c>
@@ -1047,8 +1373,24 @@
       <c r="K7" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="L7" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>Laptop</v>
+      </c>
+      <c r="M7" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>Profitable_order</v>
+      </c>
+      <c r="N7" s="2" t="str" cm="1">
+        <f t="array" ref="N7">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>High Sales</v>
+      </c>
+      <c r="P7" t="str" cm="1">
+        <f t="array" ref="P7">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt; 0, "Negative Sales")</f>
+        <v>High Sales</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>1007</v>
       </c>
@@ -1062,7 +1404,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>15</v>
@@ -1077,13 +1419,29 @@
         <v>21000</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="L8" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>Mobile</v>
+      </c>
+      <c r="M8" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>Profitable_order</v>
+      </c>
+      <c r="N8" s="2" t="str" cm="1">
+        <f t="array" ref="N8">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>Medium Sales</v>
+      </c>
+      <c r="P8" t="str" cm="1">
+        <f t="array" ref="P8">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt; 0, "Negative Sales")</f>
+        <v>Medium Sales</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>1008</v>
       </c>
@@ -1109,7 +1467,7 @@
         <v>1800</v>
       </c>
       <c r="I9" s="2">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>22</v>
@@ -1117,66 +1475,213 @@
       <c r="K9" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9" s="2" t="str">
+        <f>_xlfn.XLOOKUP(Table1[[#This Row],[Product_ID]],Table2[Product_ID],Table2[Product_Name],"Product does not exist",0)</f>
+        <v>Shoes</v>
+      </c>
+      <c r="M9" s="2" t="str">
+        <f>IF(OR(Table1[[#This Row],[Total_Amount]]&gt;=20000,Table1[[#This Row],[Order_Status]]="Delivered"),"Profitable_order", "incomplete order")</f>
+        <v>Profitable_order</v>
+      </c>
+      <c r="N9" s="2" t="str" cm="1">
+        <f t="array" ref="N9">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;=30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales", Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales")</f>
+        <v>Low Sales</v>
+      </c>
+      <c r="P9" t="str" cm="1">
+        <f t="array" ref="P9">_xlfn.IFS(Table1[[#This Row],[Total_Amount]]&gt;= 30000, "High Sales", Table1[[#This Row],[Total_Amount]]&gt;= 20000, "Medium Sales",Table1[[#This Row],[Total_Amount]]&lt; 20000, "Low Sales", Table1[[#This Row],[Total_Amount]]&lt;= 0, "Negative Sales")</f>
+        <v>Low Sales</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <f>SUMIFS(Table1[Total_Amount],Table1[Product_Name],"Laptop",Table1[Payment_Mode],"Card",Table1[Order_Status],"Delivered")</f>
+        <v>123000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2</v>
       </c>
       <c r="B14" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J14" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>3</v>
       </c>
       <c r="B15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>4</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16">
+        <f>SUMIF(Table1[Payment_Mode],"Card", Table1[Total_Amount])</f>
+        <v>129000</v>
+      </c>
+      <c r="J16" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>5</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17">
+        <f>SUMIF(Table1[Payment_Mode],"UPI",Table1[Total_Amount])</f>
+        <v>42300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>6</v>
       </c>
       <c r="B18" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18">
+        <f>SUMIF(Table1[Payment_Mode],"COD", Table1[Total_Amount])</f>
+        <v>6000</v>
+      </c>
+      <c r="I18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>7</v>
       </c>
       <c r="B19" t="s">
         <v>49</v>
+      </c>
+      <c r="J19" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J20" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I22" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22" t="s">
+        <v>93</v>
+      </c>
+      <c r="K22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I23" t="s">
+        <v>99</v>
+      </c>
+      <c r="J23" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <f>COUNTIF(Table1[City], "Pune")</f>
+        <v>4</v>
+      </c>
+      <c r="I25" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" t="s">
+        <v>101</v>
+      </c>
+      <c r="K25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J26" t="s">
+        <v>102</v>
+      </c>
+      <c r="K26" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1188,6 +1693,140 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380CEFD8-D48C-42BB-8383-FE36E1ED3D68}">
+  <dimension ref="B3:K9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="4">
+        <v>101</v>
+      </c>
+      <c r="D3" s="4">
+        <v>102</v>
+      </c>
+      <c r="E3" s="4">
+        <v>103</v>
+      </c>
+      <c r="F3" s="4">
+        <v>104</v>
+      </c>
+      <c r="G3" s="4">
+        <v>105</v>
+      </c>
+      <c r="K3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4">
+        <v>105</v>
+      </c>
+      <c r="K4" t="str">
+        <f>HLOOKUP(J4,B3:G7,2,FALSE)</f>
+        <v>Maria</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="4">
+        <v>34000</v>
+      </c>
+      <c r="D5" s="4">
+        <v>55000</v>
+      </c>
+      <c r="E5" s="4">
+        <v>56000</v>
+      </c>
+      <c r="F5" s="4">
+        <v>30000</v>
+      </c>
+      <c r="G5" s="4">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="4">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4">
+        <v>34</v>
+      </c>
+      <c r="F6" s="4">
+        <v>27</v>
+      </c>
+      <c r="G6" s="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="K8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="J9">
+        <v>106</v>
+      </c>
+      <c r="K9" t="str">
+        <f>_xlfn.XLOOKUP(J9,C3:G3,C7:G7,"Employee does not exist",0)</f>
+        <v>Employee does not exist</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D8E5C7-3A28-4EA9-8829-0C30CB11E1F0}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1288,4 +1927,438 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F2E7B3-9E14-4DC1-9BC3-A228F86DDA41}">
+  <dimension ref="C2:T16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="8" max="8" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C3">
+        <v>23</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D12" si="0">IF(C3&gt;=80, "Fast", "Slow")</f>
+        <v>Slow</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I12" si="1">IF(AND(F3&gt;=18, H3="Y"), "Eligible", "Not eligible")</f>
+        <v>Not eligible</v>
+      </c>
+      <c r="K3">
+        <v>34</v>
+      </c>
+      <c r="L3" t="str" cm="1">
+        <f t="array" ref="L3">_xlfn.IFS(K3&gt;=95, "A+",K3&gt;=85, "A",K3&gt;=75, "B", K3&gt;=55, "C", K3&gt;=36, "D", K3&lt;35, "Fail")</f>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="4" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <v>80</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>Fast</v>
+      </c>
+      <c r="F4">
+        <v>19</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="1"/>
+        <v>Eligible</v>
+      </c>
+      <c r="K4">
+        <v>56</v>
+      </c>
+      <c r="L4" t="str" cm="1">
+        <f t="array" ref="L4">_xlfn.IFS(K4&gt;=95, "A+",K4&gt;=85, "A",K4&gt;=75, "B", K4&gt;=55, "C", K4&gt;=36, "D", K4&lt;35, "Fail")</f>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="5" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>Slow</v>
+      </c>
+      <c r="F5">
+        <v>23</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="1"/>
+        <v>Not eligible</v>
+      </c>
+      <c r="K5">
+        <v>87</v>
+      </c>
+      <c r="L5" t="str" cm="1">
+        <f t="array" ref="L5">_xlfn.IFS(K5&gt;=95, "A+",K5&gt;=85, "A",K5&gt;=75, "B", K5&gt;=55, "C", K5&gt;=36, "D", K5&lt;35, "Fail")</f>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="6" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C6">
+        <v>34</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>Slow</v>
+      </c>
+      <c r="F6">
+        <v>14</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="1"/>
+        <v>Not eligible</v>
+      </c>
+      <c r="K6">
+        <v>23</v>
+      </c>
+      <c r="L6" t="str" cm="1">
+        <f t="array" ref="L6">_xlfn.IFS(K6&gt;=95, "A+",K6&gt;=85, "A",K6&gt;=75, "B", K6&gt;=55, "C", K6&gt;=36, "D", K6&lt;35, "Fail")</f>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="7" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>56</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>Slow</v>
+      </c>
+      <c r="F7">
+        <v>56</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="1"/>
+        <v>Not eligible</v>
+      </c>
+      <c r="K7">
+        <v>90</v>
+      </c>
+      <c r="L7" t="str" cm="1">
+        <f t="array" ref="L7">_xlfn.IFS(K7&gt;=95, "A+",K7&gt;=85, "A",K7&gt;=75, "B", K7&gt;=55, "C", K7&gt;=36, "D", K7&lt;35, "Fail")</f>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="8" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>80</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>Fast</v>
+      </c>
+      <c r="F8">
+        <v>35</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="1"/>
+        <v>Eligible</v>
+      </c>
+      <c r="K8">
+        <v>95</v>
+      </c>
+      <c r="L8" t="str" cm="1">
+        <f t="array" ref="L8">_xlfn.IFS(K8&gt;=95, "A+",K8&gt;=85, "A",K8&gt;=75, "B", K8&gt;=55, "C", K8&gt;=36, "D", K8&lt;35, "Fail")</f>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="9" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C9">
+        <v>120</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>Fast</v>
+      </c>
+      <c r="F9">
+        <v>64</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="1"/>
+        <v>Eligible</v>
+      </c>
+      <c r="K9">
+        <v>98</v>
+      </c>
+      <c r="L9" t="str" cm="1">
+        <f t="array" ref="L9">_xlfn.IFS(K9&gt;=95, "A+",K9&gt;=85, "A",K9&gt;=75, "B", K9&gt;=55, "C", K9&gt;=36, "D", K9&lt;35, "Fail")</f>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="10" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C10">
+        <v>150</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>Fast</v>
+      </c>
+      <c r="F10">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v>Not eligible</v>
+      </c>
+      <c r="K10">
+        <v>56</v>
+      </c>
+      <c r="L10" t="str" cm="1">
+        <f t="array" ref="L10">_xlfn.IFS(K10&gt;=95, "A+",K10&gt;=85, "A",K10&gt;=75, "B", K10&gt;=55, "C", K10&gt;=36, "D", K10&lt;35, "Fail")</f>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="11" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C11">
+        <v>70</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>Slow</v>
+      </c>
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="1"/>
+        <v>Eligible</v>
+      </c>
+      <c r="K11">
+        <v>45</v>
+      </c>
+      <c r="L11" t="str" cm="1">
+        <f t="array" ref="L11">_xlfn.IFS(K11&gt;=95, "A+",K11&gt;=85, "A",K11&gt;=75, "B", K11&gt;=55, "C", K11&gt;=36, "D", K11&lt;35, "Fail")</f>
+        <v>D</v>
+      </c>
+    </row>
+    <row r="12" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C12">
+        <v>300</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>Fast</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="1"/>
+        <v>Not eligible</v>
+      </c>
+      <c r="K12">
+        <v>37</v>
+      </c>
+      <c r="L12" t="str" cm="1">
+        <f t="array" ref="L12">_xlfn.IFS(K12&gt;=95, "A+",K12&gt;=85, "A",K12&gt;=75, "B", K12&gt;=55, "C", K12&gt;=36, "D", K12&lt;35, "Fail")</f>
+        <v>D</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>80</v>
+      </c>
+      <c r="R12" t="s">
+        <v>81</v>
+      </c>
+      <c r="S12" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="K13">
+        <v>56</v>
+      </c>
+      <c r="L13" t="str" cm="1">
+        <f t="array" ref="L13">_xlfn.IFS(K13&gt;=95, "A+",K13&gt;=85, "A",K13&gt;=75, "B", K13&gt;=55, "C", K13&gt;=36, "D", K13&lt;35, "Fail")</f>
+        <v>C</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="b">
+        <f>AND(O13,P13)</f>
+        <v>1</v>
+      </c>
+      <c r="R13" t="b">
+        <f>OR(O13,P13)</f>
+        <v>1</v>
+      </c>
+      <c r="S13" t="b">
+        <f>NOT(O13)</f>
+        <v>0</v>
+      </c>
+      <c r="T13" t="b">
+        <f>NOT(P13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="K14">
+        <v>68</v>
+      </c>
+      <c r="L14" t="str" cm="1">
+        <f t="array" ref="L14">_xlfn.IFS(K14&gt;=95, "A+",K14&gt;=85, "A",K14&gt;=75, "B", K14&gt;=55, "C", K14&gt;=36, "D", K14&lt;35, "Fail")</f>
+        <v>C</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
+        <f>AND(O14,P14)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" t="b">
+        <f t="shared" ref="R14:R16" si="2">OR(O14,P14)</f>
+        <v>1</v>
+      </c>
+      <c r="S14" t="b">
+        <f t="shared" ref="S14:S16" si="3">NOT(O14)</f>
+        <v>0</v>
+      </c>
+      <c r="T14" t="b">
+        <f t="shared" ref="T14:T16" si="4">NOT(P14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="K15">
+        <v>78</v>
+      </c>
+      <c r="L15" t="str" cm="1">
+        <f t="array" ref="L15">_xlfn.IFS(K15&gt;=95, "A+",K15&gt;=85, "A",K15&gt;=75, "B", K15&gt;=55, "C", K15&gt;=36, "D", K15&lt;35, "Fail")</f>
+        <v>B</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <f>AND(O15,P15)</f>
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="S15" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T15" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <f>AND(O16,P16)</f>
+        <v>0</v>
+      </c>
+      <c r="R16" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S16" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T16" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>